--- a/output/pdf_financials_xlsx/ZCT.xlsx
+++ b/output/pdf_financials_xlsx/ZCT.xlsx
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.004146</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.004146</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.004146</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.004146</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.052</v>
+        <v>3.047854</v>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">

--- a/output/pdf_financials_xlsx/ZCT.xlsx
+++ b/output/pdf_financials_xlsx/ZCT.xlsx
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>-0.011019</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.005602</v>
+        <v>-0.009601999999999999</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>-0.012019</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.014602</v>
+        <v>-0.018602</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5091,22 +5091,24 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>INCOME</t>
+        </is>
+      </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Professional fees $</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="n">
-        <v>0.008999999999999999</v>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F70" s="5" t="n">
-        <v>0.00925</v>
+        <v>0.031</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -5120,18 +5122,24 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>INCOME</t>
+        </is>
+      </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Legal expenses</t>
+          <t>Note 2 0 2 5 2 0 2 4 *2 0 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" s="5" t="n">
-        <v>0.002019</v>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F71" s="5" t="n">
-        <v>0.004891</v>
+        <v>0.003</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -5145,10 +5153,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>INCOME</t>
+        </is>
+      </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Recovery of expenses</t>
+          <t>Research and development expenses 9 (381) (1,223)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -5158,7 +5170,7 @@
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>-0.008539</v>
+        <v>-1.868</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -5172,22 +5184,24 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>INCOME</t>
+        </is>
+      </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="n">
-        <v>-0.011019</v>
+          <t>General and administrative expenses 10 (911) (1,018)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>-0.005602</v>
+        <v>-0.649</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -5203,20 +5217,24 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>INCOME</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>- Basic and diluted</t>
+          <t>Issuance costs in reverse acquisition 1 - (4,000)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F74" s="5" t="n">
-        <v>2</v>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -5232,26 +5250,295 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
+          <t>Net operating loss                                                      (1,292)         ) 6,241(         ) 2,517(</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Finance expense - (141)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Net operating loss                                                      (1,292)         ) 6,241(         ) 2,517(</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Finance income 262 99</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Foreign currencies translation adjustments                              43         200            ) 44(</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Total comprehensive loss )987 ( (6,083)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>-2.557</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>the Company</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>** Represent amount less than CAD</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Professional fees $</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>0.00925</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Legal expenses</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" s="5" t="n">
+        <v>0.002019</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>0.004891</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Recovery of expenses</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>-0.008539</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>-0.011019</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>-0.005602</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
           <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>- Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
         <is>
           <t>Basic and diluted loss per share $</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>BasicEPS</t>
         </is>
       </c>
-      <c r="E75" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" t="inlineStr">
+      <c r="E84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="inlineStr">
         <is>
           <t>-</t>
         </is>
